--- a/Docs/TablasDatos-Lab6.xlsx
+++ b/Docs/TablasDatos-Lab6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Universidad\2025-2\Asistencia\Laboratorios\Lab6\ISIS1225-Laboratorio-6\Docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniandes-my.sharepoint.com/personal/j_penalozar_uniandes_edu_co/Documents/Documentos/Universidad de los Andes/Semestre 5/EDA Lab/Lab 6/Laboratorio6-G07/Docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD33DA02-4501-4B58-9D83-E0FFBD1B4D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{BEB0B353-C102-1C46-8718-1DAA0F06B822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="767" xr2:uid="{D82936D8-D2C9-4EB2-9CBC-3665F65B95FD}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="767" xr2:uid="{D82936D8-D2C9-4EB2-9CBC-3665F65B95FD}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos Lab6" sheetId="1" r:id="rId1"/>
@@ -455,7 +455,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -590,6 +590,12 @@
             <c:dispRSqr val="1"/>
             <c:dispEq val="1"/>
             <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-2.9307698912734669E-2"/>
+                  <c:y val="-9.6907253204515775E-3"/>
+                </c:manualLayout>
+              </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
               <c:spPr>
                 <a:noFill/>
@@ -626,6 +632,18 @@
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>767215.9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>438455.27</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>414779.85</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>400669.87</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -635,6 +653,18 @@
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>3723.55</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2986.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3124.17</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3488.32</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -733,6 +763,18 @@
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>412658.61</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>400588.52</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>397036.16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>395828.64</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -742,6 +784,18 @@
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2686.87</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2746.27</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2917.73</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3099.23</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -1079,7 +1133,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1241,8 +1295,8 @@
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="0.11507708357000557"/>
-                  <c:y val="-8.8873837694404562E-3"/>
+                  <c:x val="-3.0602455130701596E-2"/>
+                  <c:y val="-8.8556830348757876E-3"/>
                 </c:manualLayout>
               </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
@@ -1299,6 +1353,18 @@
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>767215.9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>438455.27</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>414779.85</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>400669.87</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -1445,6 +1511,18 @@
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>412658.61</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>400588.52</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>397036.16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>395828.64</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -2839,7 +2917,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9297051" cy="6073205"/>
+    <xdr:ext cx="8676355" cy="6290654"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
@@ -2872,7 +2950,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9297051" cy="6073205"/>
+    <xdr:ext cx="8681493" cy="6293134"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
@@ -3220,24 +3298,46 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{0FEE0C4C-5260-5D48-A63A-22E15E37B24C}">
+  <we:reference id="WA200009404" version="1.0.0.8" store="Omex" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="WA200009404" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;d02ca656-0ca8-489a-ace4-1938d2051ba1&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5B14742-4EBB-4241-AC8A-0E5F24F7BB7B}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="27.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.1640625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
     </row>
-    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -3248,42 +3348,58 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="8">
         <v>0.1</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="7"/>
+      <c r="B3" s="5">
+        <v>767215.9</v>
+      </c>
+      <c r="C3" s="7">
+        <v>3723.55</v>
+      </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="9">
         <v>0.5</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="7"/>
+      <c r="B4" s="2">
+        <v>438455.27</v>
+      </c>
+      <c r="C4" s="7">
+        <v>2986.25</v>
+      </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="8">
         <v>0.7</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="7"/>
+      <c r="B5" s="2">
+        <v>414779.85</v>
+      </c>
+      <c r="C5" s="7">
+        <v>3124.17</v>
+      </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
         <v>0.9</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="7"/>
+      <c r="B6" s="2">
+        <v>400669.87</v>
+      </c>
+      <c r="C6" s="7">
+        <v>3488.32</v>
+      </c>
     </row>
-    <row r="9" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
     </row>
-    <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
@@ -3294,35 +3410,51 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>2</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="5"/>
+      <c r="B11" s="2">
+        <v>412658.61</v>
+      </c>
+      <c r="C11" s="5">
+        <v>2686.87</v>
+      </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>4</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
+      <c r="B12" s="2">
+        <v>400588.52</v>
+      </c>
+      <c r="C12" s="2">
+        <v>2746.27</v>
+      </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>6</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
+      <c r="B13" s="2">
+        <v>397036.16</v>
+      </c>
+      <c r="C13" s="2">
+        <v>2917.73</v>
+      </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>8</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
+      <c r="B14" s="2">
+        <v>395828.64</v>
+      </c>
+      <c r="C14" s="2">
+        <v>3099.23</v>
+      </c>
     </row>
-    <row r="23" ht="14.65" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" ht="14.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
@@ -3348,6 +3480,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010023858CF01A2EF24688B692775F4C60A4" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="af74a0f8eb440a60883e9dd833f0742f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="164883f8-7691-4ecf-b54a-664c0d0edefe" xmlns:ns3="85e30bcc-d76c-4413-8e4d-2dce22fb0743" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f5ceeff32ffca1089660572a8ebd1782" ns2:_="" ns3:_="">
     <xsd:import namespace="164883f8-7691-4ecf-b54a-664c0d0edefe"/>
@@ -3596,27 +3737,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97C5E1E0-C817-4769-9D2D-1DC296B681FA}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="85e30bcc-d76c-4413-8e4d-2dce22fb0743"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="164883f8-7691-4ecf-b54a-664c0d0edefe"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="85e30bcc-d76c-4413-8e4d-2dce22fb0743"/>
-    <ds:schemaRef ds:uri="164883f8-7691-4ecf-b54a-664c0d0edefe"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8DF3742-38F2-4B99-B335-CC4F04ED9F45}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E10B9E65-6C88-4633-81F7-F02338B2B10B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3633,12 +3779,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8DF3742-38F2-4B99-B335-CC4F04ED9F45}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Docs/TablasDatos-Lab6.xlsx
+++ b/Docs/TablasDatos-Lab6.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="14_{BEB0B353-C102-1C46-8718-1DAA0F06B822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="767" xr2:uid="{D82936D8-D2C9-4EB2-9CBC-3665F65B95FD}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="767" activeTab="1" xr2:uid="{D82936D8-D2C9-4EB2-9CBC-3665F65B95FD}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos Lab6" sheetId="1" r:id="rId1"/>
